--- a/artfynd/A 32068-2024 artfynd.xlsx
+++ b/artfynd/A 32068-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103401910</v>
+        <v>103995898</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551799.2789872676</v>
+        <v>551829</v>
       </c>
       <c r="R2" t="n">
-        <v>7017203.469469346</v>
+        <v>7017126</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-21</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-21</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,53 +766,57 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103401909</v>
+        <v>103995956</v>
       </c>
       <c r="B3" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551742.9282012931</v>
+        <v>551973</v>
       </c>
       <c r="R3" t="n">
-        <v>7017063.924114399</v>
+        <v>7017008</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-21</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-21</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,53 +882,57 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103401913</v>
+        <v>103401916</v>
       </c>
       <c r="B4" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551873.8952161985</v>
+        <v>551677</v>
       </c>
       <c r="R4" t="n">
-        <v>7017076.385923319</v>
+        <v>7017147</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +975,9 @@
           <t>2022-08-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103995957</v>
+        <v>103401913</v>
       </c>
       <c r="B5" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551944.4255722223</v>
+        <v>551874</v>
       </c>
       <c r="R5" t="n">
-        <v>7017007.302038759</v>
+        <v>7017076</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1069,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,40 +1085,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103995855</v>
+        <v>103995954</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551944.3601893287</v>
+        <v>551790</v>
       </c>
       <c r="R6" t="n">
-        <v>7017011.352277414</v>
+        <v>7017201</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1171,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1181,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,37 +1217,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103995954</v>
+        <v>103401909</v>
       </c>
       <c r="B7" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551790.3029540351</v>
+        <v>551743</v>
       </c>
       <c r="R7" t="n">
-        <v>7017201.07439526</v>
+        <v>7017064</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,22 +1282,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:54</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:54</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,40 +1298,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103995898</v>
+        <v>103401912</v>
       </c>
       <c r="B8" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,21 +1325,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1414,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551829.3794553973</v>
+        <v>551805</v>
       </c>
       <c r="R8" t="n">
-        <v>7017125.633053874</v>
+        <v>7017209</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,22 +1379,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,40 +1395,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103995947</v>
+        <v>103995924</v>
       </c>
       <c r="B9" t="n">
-        <v>94440</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>551812.6570071685</v>
+        <v>551973</v>
       </c>
       <c r="R9" t="n">
-        <v>7017156.422342596</v>
+        <v>7017043</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1481,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1491,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,15 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103995891</v>
+        <v>103995947</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,21 +1538,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1841</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551921.829044085</v>
+        <v>551813</v>
       </c>
       <c r="R10" t="n">
-        <v>7017066.805941355</v>
+        <v>7017157</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,7 +1597,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1607,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,11 +1618,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -1742,37 +1643,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103995929</v>
+        <v>103401910</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1782,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>551873.960510734</v>
+        <v>551799</v>
       </c>
       <c r="R11" t="n">
-        <v>7017072.335766661</v>
+        <v>7017203</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,22 +1708,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,62 +1724,48 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103995915</v>
+        <v>103995899</v>
       </c>
       <c r="B12" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1903,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551907.4222690641</v>
+        <v>551943</v>
       </c>
       <c r="R12" t="n">
-        <v>7017009.8559146</v>
+        <v>7017015</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1938,7 +1810,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1948,7 +1820,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,6 +1831,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -1984,15 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103995899</v>
+        <v>103995957</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,21 +1872,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2024,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551942.4922508611</v>
+        <v>551945</v>
       </c>
       <c r="R13" t="n">
-        <v>7017015.373412865</v>
+        <v>7017007</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2059,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2069,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2080,11 +1952,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -2110,15 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103995956</v>
+        <v>103401914</v>
       </c>
       <c r="B14" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,21 +1988,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2150,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551972.8013558576</v>
+        <v>551686</v>
       </c>
       <c r="R14" t="n">
-        <v>7017008.660521535</v>
+        <v>7017151</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2180,22 +2042,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2206,28 +2058,933 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>103995891</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>551922</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7017067</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Via Johan Staaf</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>103995929</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>551874</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7017072</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>103995934</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>551652</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7017115</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>103995844</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>551653</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7017117</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>103995918</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>551657</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7017125</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>103995855</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>551945</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7017011</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>103995915</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>551908</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7017010</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>103401907</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>551981</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7016905</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32068-2024 artfynd.xlsx
+++ b/artfynd/A 32068-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995898</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995956</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401916</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401913</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995954</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401909</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1408,6 +1443,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401912</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995924</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995947</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1737,6 +1787,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401910</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1858,6 +1913,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995899</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1974,6 +2034,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995957</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2071,6 +2136,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401914</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2192,6 +2262,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995891</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2308,6 +2383,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995929</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2424,6 +2504,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995934</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2540,6 +2625,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995844</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2656,6 +2746,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995918</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2772,6 +2867,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995855</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2888,6 +2988,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995915</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2985,8 +3090,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401907</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>